--- a/data/trans_dic/IP24_R_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP24_R_2023-Edad-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,26; 12,82</t>
+          <t>1,01; 8,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,76; 8,75</t>
+          <t>2,53; 14,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,87; 7,75</t>
+          <t>2,23; 9,42</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,07; 8,17</t>
+          <t>4,04; 10,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,14; 10,55</t>
+          <t>3,35; 9,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,18; 8,39</t>
+          <t>4,33; 8,64</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,06%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,23; 17,59</t>
+          <t>10,12; 19,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,19; 19,86</t>
+          <t>6,32; 14,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,59; 15,92</t>
+          <t>9,01; 14,96</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>14,7%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,29; 13,16</t>
+          <t>14,33; 23,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,2; 21,68</t>
+          <t>7,49; 14,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,86; 16,66</t>
+          <t>12,13; 17,98</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>11,27%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,76; 10,96</t>
+          <t>11,37; 16,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,71; 15,15</t>
+          <t>7,13; 10,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,27; 12,27</t>
+          <t>9,79; 12,88</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>1565</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1754</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4965</t>
+          <t>4816</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1265; 7181</t>
+          <t>487; 4337</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>444; 5125</t>
+          <t>1286; 7109</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2143; 8882</t>
+          <t>2213; 9331</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>17</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>8168</t>
+          <t>10513</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>12131</t>
+          <t>8197</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20299</t>
+          <t>18711</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4892; 13012</t>
+          <t>6356; 16082</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7534; 19216</t>
+          <t>4877; 13257</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14278; 28641</t>
+          <t>13094; 26154</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>25</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18422</t>
+          <t>28452</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>29941</t>
+          <t>16631</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>48363</t>
+          <t>45083</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>12509; 30441</t>
+          <t>20158; 37921</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>21554; 42014</t>
+          <t>11040; 25074</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>36886; 61232</t>
+          <t>33696; 55919</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>41</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>26046</t>
+          <t>53790</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>52963</t>
+          <t>26928</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>79009</t>
+          <t>80718</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17315; 36242</t>
+          <t>41947; 67787</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>40332; 66242</t>
+          <t>19219; 36094</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>63088; 96759</t>
+          <t>66614; 98756</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>89</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>55847</t>
+          <t>94319</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>96789</t>
+          <t>55008</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>152636</t>
+          <t>149328</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>44882; 72726</t>
+          <t>79290; 113187</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>81121; 114773</t>
+          <t>44740; 67125</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>131762; 174382</t>
+          <t>129735; 170692</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP24_R_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP24_R_2023-Edad-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que hacen entrenamiento deportivo o físico varias veces por semana (tasa de respuesta: 99,43%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>3,24%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>6,4%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4,86%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>1,01; 8,99</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>2,53; 14,0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2,23; 9,42</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>3-7</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>6,69%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>5,63%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>6,18%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>4,04; 10,23</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>3,35; 9,11</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>4,33; 8,64</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>14,29%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>9,52%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>12,06%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>10,12; 19,04</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>6,32; 14,35</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>9,01; 14,96</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>12-15</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>18,38%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>10,5%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>14,7%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>14,33; 23,16</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>7,49; 14,07</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>12,13; 17,98</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>13,53%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>8,77%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>11,27%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>11,37; 16,23</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>7,13; 10,7</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>9,79; 12,88</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.03242812166230993</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.06402942245413905</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.04863106037171529</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>1565</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>3251</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>4816</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.01009078781994521</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.02533272539960553</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.0223411226707299</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>487; 4337</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1286; 7109</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2213; 9331</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.08986381656216921</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.1400042236742077</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.09422166151956181</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.06689479906648613</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.05633236120636593</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.06181676871748443</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>10513</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>8197</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>18711</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.04044348860733554</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.03351373711348438</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.04325910059558802</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>6356; 16082</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>4877; 13257</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>13094; 26154</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.1023244960097905</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.09109980710282596</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.08640862636380335</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.142855834902994</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.0952140472440567</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.1205955180457038</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>28452</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>16631</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>45083</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.1012149668911502</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.06320552058532108</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.09013596115099122</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>20158; 37921</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>11040; 25074</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>33696; 55919</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.190401474358405</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.1435465365574038</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.1495829195928004</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.1838052094953168</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.104961592020412</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.1469740610811961</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>53790</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>26928</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>80718</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.1433380118370305</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.07491426111495281</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.1212934641476035</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>41947; 67787</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>19219; 36094</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>66614; 98756</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.231636054836397</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.1406875014558921</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.1798178136573854</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.1352778258670091</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.08765936611695602</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.1127213983778644</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>94319</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>55008</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>149328</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.1137212710526864</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.07129659071047194</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.09793194771502396</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>79290; 113187</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>44740; 67125</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>129735; 170692</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.1623384425302957</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.1069691538419971</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.1288486158986255</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que hacen entrenamiento deportivo o físico varias veces por semana (tasa de respuesta: 99,43%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>1565</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>3251</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>4816</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>487</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>1286</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>2213</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>4337</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>7109</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>9331</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>10513</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>8197</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>18711</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>6356</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>4877</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>13094</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>16082</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>13257</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>26154</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>28452</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>16631</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>45083</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>20158</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>11040</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>33696</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>37921</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>25074</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>55919</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>53790</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>26928</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>80718</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>41947</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>19219</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>66614</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>67787</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>36094</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>98756</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>124</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>89</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>94319</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>55008</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>149328</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>79290</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>44740</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>129735</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>113187</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>67125</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>170692</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>